--- a/docs/test_models/warrior-cats-actions.xlsx
+++ b/docs/test_models/warrior-cats-actions.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="85">
   <si>
     <t>action</t>
   </si>
@@ -86,7 +86,7 @@
     <t>recipient_scope</t>
   </si>
   <si>
-    <t>scouting</t>
+    <t>combat</t>
   </si>
   <si>
     <t>all</t>
@@ -96,9 +96,6 @@
   </si>
   <si>
     <t>healing</t>
-  </si>
-  <si>
-    <t>combat</t>
   </si>
   <si>
     <t>winners_only</t>
@@ -975,13 +972,13 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1093,7 +1090,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C8">
         <v>80</v>
@@ -1121,13 +1118,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C10">
         <v>150</v>
       </c>
       <c r="D10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1135,13 +1132,13 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C11">
         <v>60</v>
       </c>
       <c r="D11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1169,7 +1166,7 @@
         <v>60</v>
       </c>
       <c r="D13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1183,7 +1180,7 @@
         <v>60</v>
       </c>
       <c r="D14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1191,13 +1188,13 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C15">
         <v>60</v>
       </c>
       <c r="D15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1205,13 +1202,13 @@
         <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C16">
         <v>60</v>
       </c>
       <c r="D16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1219,24 +1216,24 @@
         <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C17">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D17" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C18">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="D18" t="s">
         <v>24</v>
@@ -1247,10 +1244,10 @@
         <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C19">
-        <v>120</v>
+        <v>15</v>
       </c>
       <c r="D19" t="s">
         <v>24</v>
@@ -1258,13 +1255,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C20">
-        <v>15</v>
+        <v>125</v>
       </c>
       <c r="D20" t="s">
         <v>24</v>
@@ -1275,10 +1272,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C21">
-        <v>125</v>
+        <v>20</v>
       </c>
       <c r="D21" t="s">
         <v>24</v>
@@ -1286,13 +1283,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C22">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="D22" t="s">
         <v>24</v>
@@ -1303,10 +1300,10 @@
         <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="D23" t="s">
         <v>24</v>
@@ -1314,13 +1311,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C24">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="D24" t="s">
         <v>24</v>
@@ -1331,10 +1328,10 @@
         <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C25">
-        <v>120</v>
+        <v>15</v>
       </c>
       <c r="D25" t="s">
         <v>24</v>
@@ -1342,13 +1339,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C26">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="D26" t="s">
         <v>24</v>
@@ -1359,10 +1356,10 @@
         <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C27">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="D27" t="s">
         <v>24</v>
@@ -1370,13 +1367,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C28">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="D28" t="s">
         <v>24</v>
@@ -1387,32 +1384,18 @@
         <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C29">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="D29" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>19</v>
-      </c>
-      <c r="B30" t="s">
-        <v>25</v>
-      </c>
-      <c r="C30">
-        <v>10</v>
-      </c>
-      <c r="D30" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -1432,134 +1415,134 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="B2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" t="s">
         <v>35</v>
       </c>
-      <c r="C2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
       <c r="B4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" t="s">
         <v>38</v>
       </c>
-      <c r="C4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
       <c r="B5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" t="s">
         <v>40</v>
       </c>
-      <c r="C5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1567,10 +1550,10 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" t="s">
         <v>49</v>
-      </c>
-      <c r="D13" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1578,10 +1561,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1589,10 +1572,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1600,10 +1583,10 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1611,10 +1594,10 @@
         <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1622,10 +1605,10 @@
         <v>13</v>
       </c>
       <c r="B18" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" t="s">
         <v>55</v>
-      </c>
-      <c r="D18" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1633,10 +1616,10 @@
         <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1644,10 +1627,10 @@
         <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1655,10 +1638,10 @@
         <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1666,10 +1649,10 @@
         <v>13</v>
       </c>
       <c r="B22" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1677,21 +1660,21 @@
         <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1708,10 +1691,10 @@
         <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -1725,29 +1708,29 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -1756,23 +1739,9 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -1791,25 +1760,25 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1823,16 +1792,16 @@
         <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" t="s">
         <v>72</v>
-      </c>
-      <c r="G2" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1843,19 +1812,19 @@
         <v>13</v>
       </c>
       <c r="C3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" t="s">
         <v>74</v>
       </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" t="s">
-        <v>75</v>
-      </c>
       <c r="G3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1863,22 +1832,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" t="s">
         <v>76</v>
       </c>
-      <c r="E4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>77</v>
-      </c>
-      <c r="G4" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1886,22 +1855,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
         <v>27</v>
       </c>
-      <c r="C5" t="s">
-        <v>28</v>
-      </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1909,22 +1878,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1935,19 +1904,19 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1955,22 +1924,22 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1978,22 +1947,22 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2001,22 +1970,22 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2024,22 +1993,22 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2047,22 +2016,22 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -2070,22 +2039,22 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -2093,233 +2062,233 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E22" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E23" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>